--- a/artfynd/A 10480-2023 artfynd.xlsx
+++ b/artfynd/A 10480-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10480-2023 artfynd.xlsx
+++ b/artfynd/A 10480-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97356840</v>
+        <v>97356835</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479266.142233011</v>
+        <v>479298</v>
       </c>
       <c r="R2" t="n">
-        <v>6437891.449269321</v>
+        <v>6437943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97356842</v>
+        <v>97356840</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479244.708881918</v>
+        <v>479266</v>
       </c>
       <c r="R3" t="n">
-        <v>6437845.027456501</v>
+        <v>6437892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97356835</v>
+        <v>97356842</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +890,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479298.7275948025</v>
+        <v>479245</v>
       </c>
       <c r="R4" t="n">
-        <v>6437943.100443725</v>
+        <v>6437845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +984,7 @@
         <v>97356841</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479284.5823213076</v>
+        <v>479284</v>
       </c>
       <c r="R5" t="n">
-        <v>6437871.78811054</v>
+        <v>6437872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1146,12 +1086,7 @@
         <v>97356836</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479296.5810474589</v>
+        <v>479297</v>
       </c>
       <c r="R6" t="n">
-        <v>6437937.823805166</v>
+        <v>6437938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 10480-2023 artfynd.xlsx
+++ b/artfynd/A 10480-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356840</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356841</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>